--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="158" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E536ABD9-EB31-4E9B-B5CF-8E452BFDD949}"/>
+  <xr:revisionPtr revIDLastSave="164" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57F78D33-0421-4F23-AFF1-314C5E9495B7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7658" uniqueCount="3280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7661" uniqueCount="3280">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -17798,7 +17798,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E100"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
@@ -18386,7 +18386,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="31.5">
+    <row r="35" spans="1:5">
       <c r="A35" s="48" t="s">
         <v>3114</v>
       </c>
@@ -19219,7 +19219,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="47.25">
+    <row r="84" spans="1:5" ht="31.5">
       <c r="A84" s="60" t="s">
         <v>3257</v>
       </c>
@@ -19355,7 +19355,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="47.25">
+    <row r="92" spans="1:5" ht="31.5">
       <c r="A92" s="60" t="s">
         <v>3266</v>
       </c>
@@ -19491,7 +19491,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="31.5">
+    <row r="100" spans="1:5">
       <c r="A100" s="60" t="s">
         <v>3278</v>
       </c>
@@ -19506,6 +19506,23 @@
       </c>
       <c r="E100" s="49">
         <v>62</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" s="60" t="s">
+        <v>3200</v>
+      </c>
+      <c r="B101" s="60" t="s">
+        <v>3201</v>
+      </c>
+      <c r="C101" s="58" t="s">
+        <v>394</v>
+      </c>
+      <c r="D101" s="50">
+        <v>46276</v>
+      </c>
+      <c r="E101" s="49">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -38643,7 +38660,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.5">
+    <row r="43" spans="1:5" ht="15.75">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -39765,7 +39782,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="47.25">
+    <row r="109" spans="1:5" ht="31.5">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="164" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57F78D33-0421-4F23-AFF1-314C5E9495B7}"/>
+  <xr:revisionPtr revIDLastSave="171" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{146A549C-738F-409B-A1A1-6536545E9E51}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7661" uniqueCount="3280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7671" uniqueCount="3283">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14281,6 +14281,15 @@
   </si>
   <si>
     <t>11/9/26 and 12/31/26</t>
+  </si>
+  <si>
+    <t>Banker Steel, a Division of Schuff Steel</t>
+  </si>
+  <si>
+    <t>Barrette Outdoor Living</t>
+  </si>
+  <si>
+    <t>12/13/26 - 12/14/26</t>
   </si>
 </sst>
 </file>
@@ -17798,7 +17807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E104"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
@@ -19523,6 +19532,57 @@
       </c>
       <c r="E101" s="49">
         <v>98</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="31.5">
+      <c r="A102" s="63" t="s">
+        <v>3280</v>
+      </c>
+      <c r="B102" s="63" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C102" s="64" t="s">
+        <v>394</v>
+      </c>
+      <c r="D102" s="65">
+        <v>46370</v>
+      </c>
+      <c r="E102" s="63">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" s="48" t="s">
+        <v>3281</v>
+      </c>
+      <c r="B103" s="48" t="s">
+        <v>3009</v>
+      </c>
+      <c r="C103" s="49" t="s">
+        <v>394</v>
+      </c>
+      <c r="D103" s="50" t="s">
+        <v>3282</v>
+      </c>
+      <c r="E103" s="48">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="63">
+      <c r="A104" s="60" t="s">
+        <v>3248</v>
+      </c>
+      <c r="B104" s="60" t="s">
+        <v>1500</v>
+      </c>
+      <c r="C104" s="58" t="s">
+        <v>394</v>
+      </c>
+      <c r="D104" s="50">
+        <v>46381</v>
+      </c>
+      <c r="E104" s="49">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -38660,7 +38720,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.75">
+    <row r="43" spans="1:5" ht="31.5">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -39782,7 +39842,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="31.5">
+    <row r="109" spans="1:5" ht="47.25">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="171" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{146A549C-738F-409B-A1A1-6536545E9E51}"/>
+  <xr:revisionPtr revIDLastSave="177" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8C62B28-E1E6-4D77-AD79-6EDD80D7DC55}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7671" uniqueCount="3283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7675" uniqueCount="3285">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14290,6 +14290,12 @@
   </si>
   <si>
     <t>12/13/26 - 12/14/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wonder Group, Inc. </t>
+  </si>
+  <si>
+    <t>9/16/26 - 1/8/27</t>
   </si>
 </sst>
 </file>
@@ -17807,7 +17813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E104"/>
+  <dimension ref="A1:E105"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
@@ -19583,6 +19589,23 @@
       </c>
       <c r="E104" s="49">
         <v>91</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" s="60" t="s">
+        <v>3283</v>
+      </c>
+      <c r="B105" s="60" t="s">
+        <v>2036</v>
+      </c>
+      <c r="C105" s="58" t="s">
+        <v>394</v>
+      </c>
+      <c r="D105" s="50" t="s">
+        <v>3284</v>
+      </c>
+      <c r="E105" s="49">
+        <v>533</v>
       </c>
     </row>
   </sheetData>
@@ -57791,7 +57814,7 @@
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="16" fitToHeight="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="19" fitToHeight="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>
@@ -59196,7 +59219,7 @@
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="15" fitToHeight="12" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="16" fitToHeight="12" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="177" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8C62B28-E1E6-4D77-AD79-6EDD80D7DC55}"/>
+  <xr:revisionPtr revIDLastSave="178" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFC3F50F-5ABB-49A9-8510-917921BA0203}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19585,7 +19585,7 @@
         <v>394</v>
       </c>
       <c r="D104" s="50">
-        <v>46381</v>
+        <v>46371</v>
       </c>
       <c r="E104" s="49">
         <v>91</v>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="178" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFC3F50F-5ABB-49A9-8510-917921BA0203}"/>
+  <xr:revisionPtr revIDLastSave="184" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{952FD519-45A6-4799-9FCA-C73ED351A870}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7675" uniqueCount="3285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7678" uniqueCount="3286">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14296,6 +14296,9 @@
   </si>
   <si>
     <t>9/16/26 - 1/8/27</t>
+  </si>
+  <si>
+    <t>Johnson &amp; Johnson Services Inc</t>
   </si>
 </sst>
 </file>
@@ -17813,7 +17816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:E106"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
@@ -19606,6 +19609,23 @@
       </c>
       <c r="E105" s="49">
         <v>533</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="31.5">
+      <c r="A106" s="60" t="s">
+        <v>3285</v>
+      </c>
+      <c r="B106" s="60" t="s">
+        <v>2937</v>
+      </c>
+      <c r="C106" s="58" t="s">
+        <v>394</v>
+      </c>
+      <c r="D106" s="50">
+        <v>46374</v>
+      </c>
+      <c r="E106" s="49">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -38743,7 +38763,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.5">
+    <row r="43" spans="1:5" ht="15.75">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -39865,7 +39885,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="47.25">
+    <row r="109" spans="1:5" ht="31.5">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="184" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{952FD519-45A6-4799-9FCA-C73ED351A870}"/>
+  <xr:revisionPtr revIDLastSave="185" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0943DA9-381B-4003-84ED-0C9A8D1EB032}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7678" uniqueCount="3286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7682" uniqueCount="3287">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14299,6 +14299,9 @@
   </si>
   <si>
     <t>Johnson &amp; Johnson Services Inc</t>
+  </si>
+  <si>
+    <t>12/17/26 - 5/21/27</t>
   </si>
 </sst>
 </file>
@@ -17816,13 +17819,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E106"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <dimension ref="A1:E107"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" style="41" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" style="33" customWidth="1"/>
+    <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" style="41" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.88671875" style="33" customWidth="1"/>
     <col min="5" max="5" width="20" style="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17860,7 +17863,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="31.5">
+    <row r="3" spans="1:5" ht="31.2">
       <c r="A3" s="60" t="s">
         <v>3151</v>
       </c>
@@ -17911,7 +17914,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="47.25">
+    <row r="6" spans="1:5" ht="46.8">
       <c r="A6" s="60" t="s">
         <v>3156</v>
       </c>
@@ -17928,7 +17931,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="47.25">
+    <row r="7" spans="1:5" ht="46.8">
       <c r="A7" s="60" t="s">
         <v>3158</v>
       </c>
@@ -17945,7 +17948,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="31.5">
+    <row r="8" spans="1:5" ht="31.2">
       <c r="A8" s="60" t="s">
         <v>3161</v>
       </c>
@@ -17962,7 +17965,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.5">
+    <row r="9" spans="1:5" ht="31.2">
       <c r="A9" s="60" t="s">
         <v>3164</v>
       </c>
@@ -17979,7 +17982,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="78.75">
+    <row r="10" spans="1:5" ht="78">
       <c r="A10" s="48" t="s">
         <v>3110</v>
       </c>
@@ -18030,7 +18033,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="47.25">
+    <row r="13" spans="1:5" ht="46.8">
       <c r="A13" s="48" t="s">
         <v>3169</v>
       </c>
@@ -18047,7 +18050,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="31.5">
+    <row r="14" spans="1:5" ht="31.2">
       <c r="A14" s="60" t="s">
         <v>3172</v>
       </c>
@@ -18132,7 +18135,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.5">
+    <row r="19" spans="1:5" ht="31.2">
       <c r="A19" s="48" t="s">
         <v>3178</v>
       </c>
@@ -18200,7 +18203,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="63">
+    <row r="23" spans="1:5" ht="62.4">
       <c r="A23" s="63" t="s">
         <v>2870</v>
       </c>
@@ -18217,7 +18220,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="31.5">
+    <row r="24" spans="1:5" ht="31.2">
       <c r="A24" s="48" t="s">
         <v>3184</v>
       </c>
@@ -18234,7 +18237,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="47.25">
+    <row r="25" spans="1:5" ht="46.8">
       <c r="A25" s="60" t="s">
         <v>3057</v>
       </c>
@@ -18319,7 +18322,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="31.5">
+    <row r="30" spans="1:5" ht="31.2">
       <c r="A30" s="60" t="s">
         <v>3193</v>
       </c>
@@ -18625,7 +18628,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.5">
+    <row r="48" spans="1:5" ht="31.2">
       <c r="A48" s="48" t="s">
         <v>3217</v>
       </c>
@@ -18846,7 +18849,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="31.5">
+    <row r="61" spans="1:5" ht="31.2">
       <c r="A61" s="63" t="s">
         <v>3231</v>
       </c>
@@ -18914,7 +18917,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="31.5">
+    <row r="65" spans="1:5" ht="31.2">
       <c r="A65" s="63" t="s">
         <v>3235</v>
       </c>
@@ -18982,7 +18985,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.5">
+    <row r="69" spans="1:5" ht="31.2">
       <c r="A69" s="60" t="s">
         <v>3239</v>
       </c>
@@ -19033,7 +19036,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="31.5">
+    <row r="72" spans="1:5" ht="31.2">
       <c r="A72" s="60" t="s">
         <v>3243</v>
       </c>
@@ -19050,7 +19053,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="31.5">
+    <row r="73" spans="1:5" ht="31.2">
       <c r="A73" s="60" t="s">
         <v>3243</v>
       </c>
@@ -19067,7 +19070,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="31.5">
+    <row r="74" spans="1:5" ht="31.2">
       <c r="A74" s="63" t="s">
         <v>3244</v>
       </c>
@@ -19084,7 +19087,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="31.5">
+    <row r="75" spans="1:5" ht="31.2">
       <c r="A75" s="48" t="s">
         <v>3245</v>
       </c>
@@ -19118,7 +19121,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="63">
+    <row r="77" spans="1:5" ht="62.4">
       <c r="A77" s="60" t="s">
         <v>3248</v>
       </c>
@@ -19186,7 +19189,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.5">
+    <row r="81" spans="1:5" ht="31.2">
       <c r="A81" s="60" t="s">
         <v>3253</v>
       </c>
@@ -19237,7 +19240,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="31.5">
+    <row r="84" spans="1:5" ht="31.2">
       <c r="A84" s="60" t="s">
         <v>3257</v>
       </c>
@@ -19254,7 +19257,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="31.5">
+    <row r="85" spans="1:5" ht="31.2">
       <c r="A85" s="60" t="s">
         <v>3258</v>
       </c>
@@ -19271,7 +19274,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="31.5">
+    <row r="86" spans="1:5" ht="31.2">
       <c r="A86" s="60" t="s">
         <v>3243</v>
       </c>
@@ -19288,7 +19291,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="31.5">
+    <row r="87" spans="1:5" ht="31.2">
       <c r="A87" s="60" t="s">
         <v>3231</v>
       </c>
@@ -19373,7 +19376,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="31.5">
+    <row r="92" spans="1:5" ht="31.2">
       <c r="A92" s="60" t="s">
         <v>3266</v>
       </c>
@@ -19543,7 +19546,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="31.5">
+    <row r="102" spans="1:5" ht="31.2">
       <c r="A102" s="63" t="s">
         <v>3280</v>
       </c>
@@ -19577,7 +19580,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="63">
+    <row r="104" spans="1:5" ht="62.4">
       <c r="A104" s="60" t="s">
         <v>3248</v>
       </c>
@@ -19611,7 +19614,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="31.5">
+    <row r="106" spans="1:5" ht="31.2">
       <c r="A106" s="60" t="s">
         <v>3285</v>
       </c>
@@ -19626,6 +19629,23 @@
       </c>
       <c r="E106" s="49">
         <v>87</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" s="48" t="s">
+        <v>2870</v>
+      </c>
+      <c r="B107" s="48" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C107" s="49" t="s">
+        <v>394</v>
+      </c>
+      <c r="D107" s="50" t="s">
+        <v>3286</v>
+      </c>
+      <c r="E107" s="48">
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -19644,12 +19664,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E86"/>
-  <sheetFormatPr defaultColWidth="20.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="20.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="50.88671875" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20604,7 +20624,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="30">
+    <row r="57" spans="1:5" ht="28.8">
       <c r="A57" s="2" t="s">
         <v>719</v>
       </c>
@@ -20723,7 +20743,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="30">
+    <row r="64" spans="1:5" ht="28.8">
       <c r="A64" s="2" t="s">
         <v>728</v>
       </c>
@@ -21134,12 +21154,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E57"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="58.85546875" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="58.88671875" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -21176,7 +21196,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="30">
+    <row r="3" spans="1:5" ht="28.8">
       <c r="A3" s="2" t="s">
         <v>752</v>
       </c>
@@ -21210,7 +21230,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30">
+    <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
         <v>755</v>
       </c>
@@ -21329,7 +21349,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="30">
+    <row r="12" spans="1:5" ht="28.8">
       <c r="A12" s="2" t="s">
         <v>764</v>
       </c>
@@ -21397,7 +21417,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30">
+    <row r="16" spans="1:5" ht="28.8">
       <c r="A16" s="2" t="s">
         <v>769</v>
       </c>
@@ -21431,7 +21451,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="30">
+    <row r="18" spans="1:5" ht="28.8">
       <c r="A18" s="2" t="s">
         <v>771</v>
       </c>
@@ -21873,7 +21893,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5" ht="28.8">
       <c r="A44" s="2" t="s">
         <v>654</v>
       </c>
@@ -22131,12 +22151,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E170"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -22241,7 +22261,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5" ht="28.8">
       <c r="A7" s="2" t="s">
         <v>817</v>
       </c>
@@ -22309,7 +22329,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="30">
+    <row r="11" spans="1:5" ht="28.8">
       <c r="A11" s="2" t="s">
         <v>819</v>
       </c>
@@ -22360,7 +22380,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="30">
+    <row r="14" spans="1:5" ht="28.8">
       <c r="A14" s="2" t="s">
         <v>764</v>
       </c>
@@ -22428,7 +22448,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="30">
+    <row r="18" spans="1:5" ht="28.8">
       <c r="A18" s="2" t="s">
         <v>824</v>
       </c>
@@ -22802,7 +22822,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="2" t="s">
         <v>841</v>
       </c>
@@ -22870,7 +22890,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5">
       <c r="A44" s="2" t="s">
         <v>846</v>
       </c>
@@ -23040,7 +23060,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="30">
+    <row r="54" spans="1:5">
       <c r="A54" s="2" t="s">
         <v>853</v>
       </c>
@@ -23295,7 +23315,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="30">
+    <row r="69" spans="1:5" ht="28.8">
       <c r="A69" s="2" t="s">
         <v>871</v>
       </c>
@@ -23686,7 +23706,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="30">
+    <row r="92" spans="1:5" ht="28.8">
       <c r="A92" s="2" t="s">
         <v>906</v>
       </c>
@@ -23754,7 +23774,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="30">
+    <row r="96" spans="1:5" ht="28.8">
       <c r="A96" s="2" t="s">
         <v>912</v>
       </c>
@@ -23856,7 +23876,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="45">
+    <row r="102" spans="1:5" ht="28.8">
       <c r="A102" s="2" t="s">
         <v>922</v>
       </c>
@@ -23873,7 +23893,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="30">
+    <row r="103" spans="1:5" ht="28.8">
       <c r="A103" s="2" t="s">
         <v>924</v>
       </c>
@@ -23924,7 +23944,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="30">
+    <row r="106" spans="1:5" ht="28.8">
       <c r="A106" s="2" t="s">
         <v>929</v>
       </c>
@@ -23992,7 +24012,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="30">
+    <row r="110" spans="1:5" ht="28.8">
       <c r="A110" s="2" t="s">
         <v>935</v>
       </c>
@@ -24026,7 +24046,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="30">
+    <row r="112" spans="1:5">
       <c r="A112" s="2" t="s">
         <v>939</v>
       </c>
@@ -24094,7 +24114,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="30">
+    <row r="116" spans="1:5" ht="28.8">
       <c r="A116" s="2" t="s">
         <v>944</v>
       </c>
@@ -24128,7 +24148,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="30">
+    <row r="118" spans="1:5" ht="28.8">
       <c r="A118" s="2" t="s">
         <v>946</v>
       </c>
@@ -24145,7 +24165,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="30">
+    <row r="119" spans="1:5" ht="28.8">
       <c r="A119" s="2" t="s">
         <v>947</v>
       </c>
@@ -24213,7 +24233,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="30">
+    <row r="123" spans="1:5">
       <c r="A123" s="2" t="s">
         <v>952</v>
       </c>
@@ -24349,7 +24369,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="30">
+    <row r="131" spans="1:5">
       <c r="A131" s="2" t="s">
         <v>961</v>
       </c>
@@ -24519,7 +24539,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="30">
+    <row r="141" spans="1:5" ht="28.8">
       <c r="A141" s="2" t="s">
         <v>976</v>
       </c>
@@ -24706,7 +24726,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="30">
+    <row r="152" spans="1:5">
       <c r="A152" s="2" t="s">
         <v>993</v>
       </c>
@@ -25049,13 +25069,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E109"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="57.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="57.44140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -26112,7 +26132,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="30">
+    <row r="63" spans="1:5">
       <c r="A63" s="4" t="s">
         <v>1052</v>
       </c>
@@ -26146,7 +26166,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="30">
+    <row r="65" spans="1:5">
       <c r="A65" s="4" t="s">
         <v>1054</v>
       </c>
@@ -26265,7 +26285,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="30">
+    <row r="72" spans="1:5" ht="28.8">
       <c r="A72" s="4" t="s">
         <v>1059</v>
       </c>
@@ -26299,7 +26319,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5">
       <c r="A74" s="4" t="s">
         <v>1061</v>
       </c>
@@ -26554,7 +26574,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="30">
+    <row r="89" spans="1:5" ht="28.8">
       <c r="A89" s="4" t="s">
         <v>1075</v>
       </c>
@@ -26622,7 +26642,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="30">
+    <row r="93" spans="1:5" ht="28.8">
       <c r="A93" s="4" t="s">
         <v>1079</v>
       </c>
@@ -26931,13 +26951,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E75"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="58.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="58.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -27059,7 +27079,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="30">
+    <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
         <v>1103</v>
       </c>
@@ -27484,7 +27504,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="30">
+    <row r="33" spans="1:5" ht="28.8">
       <c r="A33" s="4" t="s">
         <v>1128</v>
       </c>
@@ -27892,7 +27912,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="30">
+    <row r="57" spans="1:5">
       <c r="A57" s="4" t="s">
         <v>1153</v>
       </c>
@@ -28235,13 +28255,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="52.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="52.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -28735,7 +28755,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="30">
+    <row r="30" spans="1:5" ht="28.8">
       <c r="A30" s="4" t="s">
         <v>1187</v>
       </c>
@@ -29109,7 +29129,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="30">
+    <row r="52" spans="1:5" ht="28.8">
       <c r="A52" s="4" t="s">
         <v>1204</v>
       </c>
@@ -29330,7 +29350,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="30">
+    <row r="65" spans="1:5">
       <c r="A65" s="4" t="s">
         <v>1218</v>
       </c>
@@ -29364,7 +29384,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5" ht="28.8">
       <c r="A67" s="4" t="s">
         <v>1196</v>
       </c>
@@ -29843,13 +29863,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="55.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="55.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -29869,7 +29889,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="30">
+    <row r="2" spans="1:5" ht="28.8">
       <c r="A2" s="4" t="s">
         <v>1240</v>
       </c>
@@ -29937,7 +29957,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30">
+    <row r="6" spans="1:5" ht="28.8">
       <c r="A6" s="4" t="s">
         <v>606</v>
       </c>
@@ -29988,7 +30008,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30">
+    <row r="9" spans="1:5" ht="28.8">
       <c r="A9" s="4" t="s">
         <v>1247</v>
       </c>
@@ -30107,7 +30127,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30">
+    <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
         <v>1256</v>
       </c>
@@ -30243,7 +30263,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="30">
+    <row r="24" spans="1:5">
       <c r="A24" s="4" t="s">
         <v>1267</v>
       </c>
@@ -30345,7 +30365,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="30">
+    <row r="30" spans="1:5" ht="28.8">
       <c r="A30" s="4" t="s">
         <v>1274</v>
       </c>
@@ -30362,7 +30382,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="30">
+    <row r="31" spans="1:5" ht="28.8">
       <c r="A31" s="4" t="s">
         <v>1275</v>
       </c>
@@ -30379,7 +30399,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="45">
+    <row r="32" spans="1:5" ht="28.8">
       <c r="A32" s="4" t="s">
         <v>1276</v>
       </c>
@@ -30481,7 +30501,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="30">
+    <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
         <v>1282</v>
       </c>
@@ -30549,7 +30569,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="30">
+    <row r="42" spans="1:5" ht="28.8">
       <c r="A42" s="4" t="s">
         <v>1287</v>
       </c>
@@ -30719,7 +30739,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="30">
+    <row r="52" spans="1:5">
       <c r="A52" s="4" t="s">
         <v>1298</v>
       </c>
@@ -30770,7 +30790,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="30">
+    <row r="55" spans="1:5">
       <c r="A55" s="4" t="s">
         <v>1303</v>
       </c>
@@ -31042,7 +31062,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="30">
+    <row r="71" spans="1:5" ht="28.8">
       <c r="A71" s="4" t="s">
         <v>817</v>
       </c>
@@ -31229,7 +31249,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="30">
+    <row r="82" spans="1:5" ht="28.8">
       <c r="A82" s="4" t="s">
         <v>1326</v>
       </c>
@@ -31555,13 +31575,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E105"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="52.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="52.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -31666,7 +31686,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
         <v>1352</v>
       </c>
@@ -33369,13 +33389,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E133"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -34500,7 +34520,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5">
       <c r="A67" s="4" t="s">
         <v>1617</v>
       </c>
@@ -34517,7 +34537,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="30">
+    <row r="68" spans="1:5">
       <c r="A68" s="4" t="s">
         <v>1619</v>
       </c>
@@ -35571,7 +35591,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="30">
+    <row r="130" spans="1:5" ht="28.8">
       <c r="A130" s="4" t="s">
         <v>1714</v>
       </c>
@@ -35630,13 +35650,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E140"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="48.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="48.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -38040,16 +38060,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E110"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" customWidth="1"/>
-    <col min="2" max="2" width="31.140625" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
-    <col min="4" max="4" width="28.28515625" customWidth="1"/>
-    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.88671875" customWidth="1"/>
+    <col min="2" max="2" width="31.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75">
+    <row r="1" spans="1:5" ht="15.6">
       <c r="A1" s="32" t="s">
         <v>59</v>
       </c>
@@ -38066,7 +38086,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="31.5">
+    <row r="2" spans="1:5" ht="31.2">
       <c r="A2" s="30" t="s">
         <v>2967</v>
       </c>
@@ -38083,7 +38103,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75">
+    <row r="3" spans="1:5" ht="15.6">
       <c r="A3" s="30" t="s">
         <v>2670</v>
       </c>
@@ -38100,7 +38120,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.5">
+    <row r="4" spans="1:5" ht="31.2">
       <c r="A4" s="34" t="s">
         <v>2970</v>
       </c>
@@ -38117,7 +38137,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="47.25">
+    <row r="5" spans="1:5" ht="46.8">
       <c r="A5" s="41" t="s">
         <v>2972</v>
       </c>
@@ -38134,7 +38154,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75">
+    <row r="6" spans="1:5" ht="15.6">
       <c r="A6" s="30" t="s">
         <v>2974</v>
       </c>
@@ -38151,7 +38171,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75">
+    <row r="7" spans="1:5" ht="15.6">
       <c r="A7" s="30" t="s">
         <v>2976</v>
       </c>
@@ -38168,7 +38188,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75">
+    <row r="8" spans="1:5" ht="15.6">
       <c r="A8" s="30" t="s">
         <v>2978</v>
       </c>
@@ -38185,7 +38205,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.5">
+    <row r="9" spans="1:5" ht="31.2">
       <c r="A9" s="30" t="s">
         <v>2979</v>
       </c>
@@ -38202,7 +38222,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75">
+    <row r="10" spans="1:5" ht="15.6">
       <c r="A10" s="30" t="s">
         <v>2982</v>
       </c>
@@ -38219,7 +38239,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="31.5">
+    <row r="11" spans="1:5" ht="31.2">
       <c r="A11" s="30" t="s">
         <v>2967</v>
       </c>
@@ -38236,7 +38256,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="94.5">
+    <row r="12" spans="1:5" ht="93.6">
       <c r="A12" s="34" t="s">
         <v>2984</v>
       </c>
@@ -38253,7 +38273,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75">
+    <row r="13" spans="1:5" ht="15.6">
       <c r="A13" s="30" t="s">
         <v>2987</v>
       </c>
@@ -38270,7 +38290,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75">
+    <row r="14" spans="1:5" ht="15.6">
       <c r="A14" s="34" t="s">
         <v>2990</v>
       </c>
@@ -38287,7 +38307,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75">
+    <row r="15" spans="1:5" ht="15.6">
       <c r="A15" s="30" t="s">
         <v>2991</v>
       </c>
@@ -38304,7 +38324,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75">
+    <row r="16" spans="1:5" ht="15.6">
       <c r="A16" s="34" t="s">
         <v>2992</v>
       </c>
@@ -38321,7 +38341,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="63">
+    <row r="17" spans="1:5" ht="62.4">
       <c r="A17" s="34" t="s">
         <v>2994</v>
       </c>
@@ -38338,7 +38358,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="63">
+    <row r="18" spans="1:5" ht="62.4">
       <c r="A18" s="34" t="s">
         <v>2997</v>
       </c>
@@ -38355,7 +38375,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.5">
+    <row r="19" spans="1:5" ht="31.2">
       <c r="A19" s="34" t="s">
         <v>2999</v>
       </c>
@@ -38372,7 +38392,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75">
+    <row r="20" spans="1:5" ht="15.6">
       <c r="A20" s="34" t="s">
         <v>2693</v>
       </c>
@@ -38389,7 +38409,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="47.25">
+    <row r="21" spans="1:5" ht="46.8">
       <c r="A21" s="34" t="s">
         <v>3002</v>
       </c>
@@ -38406,7 +38426,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75">
+    <row r="22" spans="1:5" ht="15.6">
       <c r="A22" s="30" t="s">
         <v>3004</v>
       </c>
@@ -38423,7 +38443,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.75">
+    <row r="23" spans="1:5" ht="15.6">
       <c r="A23" s="34" t="s">
         <v>3006</v>
       </c>
@@ -38440,7 +38460,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.75">
+    <row r="24" spans="1:5" ht="15.6">
       <c r="A24" s="34" t="s">
         <v>3008</v>
       </c>
@@ -38457,7 +38477,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.75">
+    <row r="25" spans="1:5" ht="15.6">
       <c r="A25" s="34" t="s">
         <v>2978</v>
       </c>
@@ -38474,7 +38494,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.75">
+    <row r="26" spans="1:5" ht="15.6">
       <c r="A26" s="30" t="s">
         <v>3010</v>
       </c>
@@ -38491,7 +38511,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="31.5">
+    <row r="27" spans="1:5" ht="31.2">
       <c r="A27" s="30" t="s">
         <v>3012</v>
       </c>
@@ -38508,7 +38528,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.75">
+    <row r="28" spans="1:5" ht="15.6">
       <c r="A28" s="34" t="s">
         <v>3014</v>
       </c>
@@ -38525,7 +38545,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.75">
+    <row r="29" spans="1:5" ht="15.6">
       <c r="A29" s="34" t="s">
         <v>3016</v>
       </c>
@@ -38542,7 +38562,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.75">
+    <row r="30" spans="1:5" ht="15.6">
       <c r="A30" s="34" t="s">
         <v>3017</v>
       </c>
@@ -38559,7 +38579,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="94.5">
+    <row r="31" spans="1:5" ht="93.6">
       <c r="A31" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38576,7 +38596,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="63">
+    <row r="32" spans="1:5" ht="62.4">
       <c r="A32" s="34" t="s">
         <v>3020</v>
       </c>
@@ -38593,7 +38613,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75">
+    <row r="33" spans="1:5" ht="15.6">
       <c r="A33" s="34" t="s">
         <v>3023</v>
       </c>
@@ -38610,7 +38630,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="63">
+    <row r="34" spans="1:5" ht="62.4">
       <c r="A34" s="34" t="s">
         <v>3024</v>
       </c>
@@ -38627,7 +38647,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.75">
+    <row r="35" spans="1:5" ht="15.6">
       <c r="A35" s="34" t="s">
         <v>3026</v>
       </c>
@@ -38644,7 +38664,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.75">
+    <row r="36" spans="1:5" ht="15.6">
       <c r="A36" s="34" t="s">
         <v>3027</v>
       </c>
@@ -38661,7 +38681,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75">
+    <row r="37" spans="1:5" ht="15.6">
       <c r="A37" s="34" t="s">
         <v>3028</v>
       </c>
@@ -38678,7 +38698,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="63">
+    <row r="38" spans="1:5" ht="62.4">
       <c r="A38" s="34" t="s">
         <v>3030</v>
       </c>
@@ -38695,7 +38715,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.75">
+    <row r="39" spans="1:5" ht="15.6">
       <c r="A39" s="34" t="s">
         <v>3032</v>
       </c>
@@ -38712,7 +38732,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.75">
+    <row r="40" spans="1:5" ht="15.6">
       <c r="A40" s="34" t="s">
         <v>3033</v>
       </c>
@@ -38729,7 +38749,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.75">
+    <row r="41" spans="1:5" ht="15.6">
       <c r="A41" s="34" t="s">
         <v>2670</v>
       </c>
@@ -38746,7 +38766,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.75">
+    <row r="42" spans="1:5" ht="15.6">
       <c r="A42" s="34" t="s">
         <v>3035</v>
       </c>
@@ -38763,7 +38783,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.75">
+    <row r="43" spans="1:5" ht="15.6">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -38780,7 +38800,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.75">
+    <row r="44" spans="1:5" ht="15.6">
       <c r="A44" s="34" t="s">
         <v>3038</v>
       </c>
@@ -38797,7 +38817,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="47.25">
+    <row r="45" spans="1:5" ht="46.8">
       <c r="A45" s="34" t="s">
         <v>3041</v>
       </c>
@@ -38814,7 +38834,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.75">
+    <row r="46" spans="1:5" ht="15.6">
       <c r="A46" s="34" t="s">
         <v>3043</v>
       </c>
@@ -38831,7 +38851,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.75">
+    <row r="47" spans="1:5" ht="15.6">
       <c r="A47" s="34" t="s">
         <v>3044</v>
       </c>
@@ -38848,7 +38868,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.5">
+    <row r="48" spans="1:5" ht="31.2">
       <c r="A48" s="34" t="s">
         <v>3046</v>
       </c>
@@ -38865,7 +38885,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.75">
+    <row r="49" spans="1:5" ht="15.6">
       <c r="A49" s="34" t="s">
         <v>3048</v>
       </c>
@@ -38882,7 +38902,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="31.5">
+    <row r="50" spans="1:5" ht="31.2">
       <c r="A50" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38899,7 +38919,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.75">
+    <row r="51" spans="1:5" ht="15.6">
       <c r="A51" s="34" t="s">
         <v>3051</v>
       </c>
@@ -38916,7 +38936,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.75">
+    <row r="52" spans="1:5" ht="15.6">
       <c r="A52" s="34" t="s">
         <v>2932</v>
       </c>
@@ -38933,7 +38953,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.75">
+    <row r="53" spans="1:5" ht="15.6">
       <c r="A53" s="34" t="s">
         <v>3055</v>
       </c>
@@ -38950,7 +38970,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="31.5">
+    <row r="54" spans="1:5" ht="31.2">
       <c r="A54" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38967,7 +38987,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.75">
+    <row r="55" spans="1:5" ht="15.6">
       <c r="A55" s="34" t="s">
         <v>3059</v>
       </c>
@@ -38984,7 +39004,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="94.5">
+    <row r="56" spans="1:5" ht="93.6">
       <c r="A56" s="34" t="s">
         <v>3060</v>
       </c>
@@ -39001,7 +39021,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.75">
+    <row r="57" spans="1:5" ht="15.6">
       <c r="A57" s="34" t="s">
         <v>3062</v>
       </c>
@@ -39018,7 +39038,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.75">
+    <row r="58" spans="1:5" ht="15.6">
       <c r="A58" s="34" t="s">
         <v>3065</v>
       </c>
@@ -39035,7 +39055,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.75">
+    <row r="59" spans="1:5" ht="15.6">
       <c r="A59" s="34" t="s">
         <v>3067</v>
       </c>
@@ -39052,7 +39072,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.75">
+    <row r="60" spans="1:5" ht="15.6">
       <c r="A60" s="34" t="s">
         <v>3071</v>
       </c>
@@ -39069,7 +39089,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="47.25">
+    <row r="61" spans="1:5" ht="46.8">
       <c r="A61" s="34" t="s">
         <v>2992</v>
       </c>
@@ -39086,7 +39106,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15.75">
+    <row r="62" spans="1:5" ht="15.6">
       <c r="A62" s="34" t="s">
         <v>2940</v>
       </c>
@@ -39103,7 +39123,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.75">
+    <row r="63" spans="1:5" ht="15.6">
       <c r="A63" s="34" t="s">
         <v>3074</v>
       </c>
@@ -39120,7 +39140,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.75">
+    <row r="64" spans="1:5" ht="15.6">
       <c r="A64" s="34" t="s">
         <v>3075</v>
       </c>
@@ -39137,7 +39157,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15.75">
+    <row r="65" spans="1:5" ht="15.6">
       <c r="A65" s="34" t="s">
         <v>3004</v>
       </c>
@@ -39154,7 +39174,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15.75">
+    <row r="66" spans="1:5" ht="15.6">
       <c r="A66" s="34" t="s">
         <v>3077</v>
       </c>
@@ -39171,7 +39191,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.75">
+    <row r="67" spans="1:5" ht="15.6">
       <c r="A67" s="34" t="s">
         <v>3079</v>
       </c>
@@ -39188,7 +39208,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.75">
+    <row r="68" spans="1:5" ht="15.6">
       <c r="A68" s="34" t="s">
         <v>3081</v>
       </c>
@@ -39205,7 +39225,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.75">
+    <row r="69" spans="1:5" ht="15.6">
       <c r="A69" s="34" t="s">
         <v>2932</v>
       </c>
@@ -39222,7 +39242,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="31.5">
+    <row r="70" spans="1:5" ht="31.2">
       <c r="A70" s="34" t="s">
         <v>2967</v>
       </c>
@@ -39239,7 +39259,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.75">
+    <row r="71" spans="1:5" ht="15.6">
       <c r="A71" s="34" t="s">
         <v>3085</v>
       </c>
@@ -39256,7 +39276,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.75">
+    <row r="72" spans="1:5" ht="15.6">
       <c r="A72" s="34" t="s">
         <v>3004</v>
       </c>
@@ -39273,7 +39293,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15.75">
+    <row r="73" spans="1:5" ht="15.6">
       <c r="A73" s="34" t="s">
         <v>3087</v>
       </c>
@@ -39290,7 +39310,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="47.25">
+    <row r="74" spans="1:5" ht="46.8">
       <c r="A74" s="34" t="s">
         <v>3057</v>
       </c>
@@ -39307,7 +39327,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.75">
+    <row r="75" spans="1:5" ht="15.6">
       <c r="A75" s="34" t="s">
         <v>2185</v>
       </c>
@@ -39324,7 +39344,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.75">
+    <row r="76" spans="1:5" ht="15.6">
       <c r="A76" s="34" t="s">
         <v>3089</v>
       </c>
@@ -39341,7 +39361,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="31.5">
+    <row r="77" spans="1:5" ht="31.2">
       <c r="A77" s="34" t="s">
         <v>3092</v>
       </c>
@@ -39358,7 +39378,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="31.5">
+    <row r="78" spans="1:5" ht="31.2">
       <c r="A78" s="34" t="s">
         <v>3099</v>
       </c>
@@ -39375,7 +39395,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="31.5">
+    <row r="79" spans="1:5" ht="31.2">
       <c r="A79" s="34" t="s">
         <v>3111</v>
       </c>
@@ -39392,7 +39412,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15.75">
+    <row r="80" spans="1:5" ht="15.6">
       <c r="A80" s="34" t="s">
         <v>3114</v>
       </c>
@@ -39409,7 +39429,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.5">
+    <row r="81" spans="1:5" ht="31.2">
       <c r="A81" s="46" t="s">
         <v>3092</v>
       </c>
@@ -39426,7 +39446,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.75">
+    <row r="82" spans="1:5" ht="15.6">
       <c r="A82" s="46" t="s">
         <v>3094</v>
       </c>
@@ -39443,7 +39463,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="31.5">
+    <row r="83" spans="1:5" ht="31.2">
       <c r="A83" s="46" t="s">
         <v>3096</v>
       </c>
@@ -39460,7 +39480,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="47.25">
+    <row r="84" spans="1:5" ht="46.8">
       <c r="A84" s="46" t="s">
         <v>3098</v>
       </c>
@@ -39477,7 +39497,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15.75">
+    <row r="85" spans="1:5" ht="15.6">
       <c r="A85" s="46" t="s">
         <v>3100</v>
       </c>
@@ -39494,7 +39514,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.75">
+    <row r="86" spans="1:5" ht="15.6">
       <c r="A86" s="47" t="s">
         <v>3102</v>
       </c>
@@ -39511,7 +39531,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15.75">
+    <row r="87" spans="1:5" ht="15.6">
       <c r="A87" s="46" t="s">
         <v>3105</v>
       </c>
@@ -39528,7 +39548,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15.75">
+    <row r="88" spans="1:5" ht="15.6">
       <c r="A88" s="46" t="s">
         <v>3107</v>
       </c>
@@ -39545,7 +39565,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15.75">
+    <row r="89" spans="1:5" ht="15.6">
       <c r="A89" s="46" t="s">
         <v>3108</v>
       </c>
@@ -39562,7 +39582,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15.75">
+    <row r="90" spans="1:5" ht="15.6">
       <c r="A90" s="46" t="s">
         <v>3110</v>
       </c>
@@ -39579,7 +39599,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="47.25">
+    <row r="91" spans="1:5" ht="46.8">
       <c r="A91" s="46" t="s">
         <v>3116</v>
       </c>
@@ -39596,7 +39616,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="31.5">
+    <row r="92" spans="1:5" ht="31.2">
       <c r="A92" s="46" t="s">
         <v>3118</v>
       </c>
@@ -39613,7 +39633,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="31.5">
+    <row r="93" spans="1:5" ht="31.2">
       <c r="A93" s="46" t="s">
         <v>3120</v>
       </c>
@@ -39630,7 +39650,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.5">
+    <row r="94" spans="1:5" ht="31.2">
       <c r="A94" s="46" t="s">
         <v>3123</v>
       </c>
@@ -39647,7 +39667,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.5">
+    <row r="95" spans="1:5" ht="31.2">
       <c r="A95" s="46" t="s">
         <v>2999</v>
       </c>
@@ -39664,7 +39684,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="15.75">
+    <row r="96" spans="1:5" ht="15.6">
       <c r="A96" s="46" t="s">
         <v>2693</v>
       </c>
@@ -39681,7 +39701,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="15.75">
+    <row r="97" spans="1:5" ht="15.6">
       <c r="A97" s="46" t="s">
         <v>3125</v>
       </c>
@@ -39698,7 +39718,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.5">
+    <row r="98" spans="1:5" ht="31.2">
       <c r="A98" s="48" t="s">
         <v>3002</v>
       </c>
@@ -39715,7 +39735,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="31.5">
+    <row r="99" spans="1:5" ht="31.2">
       <c r="A99" s="48" t="s">
         <v>3129</v>
       </c>
@@ -39732,7 +39752,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15.75">
+    <row r="100" spans="1:5" ht="15.6">
       <c r="A100" s="48" t="s">
         <v>2967</v>
       </c>
@@ -39749,7 +39769,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15.75">
+    <row r="101" spans="1:5" ht="15.6">
       <c r="A101" s="48" t="s">
         <v>2932</v>
       </c>
@@ -39766,7 +39786,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="31.5">
+    <row r="102" spans="1:5" ht="31.2">
       <c r="A102" s="48" t="s">
         <v>3132</v>
       </c>
@@ -39783,7 +39803,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15.75">
+    <row r="103" spans="1:5" ht="15.6">
       <c r="A103" s="51" t="s">
         <v>2935</v>
       </c>
@@ -39800,7 +39820,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15.75">
+    <row r="104" spans="1:5" ht="15.6">
       <c r="A104" s="48" t="s">
         <v>3134</v>
       </c>
@@ -39817,7 +39837,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15.75">
+    <row r="105" spans="1:5" ht="15.6">
       <c r="A105" s="51" t="s">
         <v>3136</v>
       </c>
@@ -39834,7 +39854,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15.75">
+    <row r="106" spans="1:5" ht="15.6">
       <c r="A106" s="48" t="s">
         <v>3138</v>
       </c>
@@ -39851,7 +39871,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15.75">
+    <row r="107" spans="1:5" ht="15.6">
       <c r="A107" s="46" t="s">
         <v>3139</v>
       </c>
@@ -39868,7 +39888,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15.75">
+    <row r="108" spans="1:5" ht="15.6">
       <c r="A108" s="34" t="s">
         <v>3144</v>
       </c>
@@ -39885,7 +39905,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="31.5">
+    <row r="109" spans="1:5" ht="31.2">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>
@@ -39902,7 +39922,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15.75">
+    <row r="110" spans="1:5" ht="15.6">
       <c r="A110" s="34" t="s">
         <v>3149</v>
       </c>
@@ -39938,14 +39958,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="35.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="35.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -41550,14 +41570,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="31.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="5" max="5" width="24.6640625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -42187,7 +42207,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="30">
+    <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
         <v>2485</v>
       </c>
@@ -43270,14 +43290,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="48.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="48.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -45009,13 +45029,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="49.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="49.109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -46753,14 +46773,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E112"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="54.5703125" style="32" customWidth="1"/>
-    <col min="2" max="2" width="50.28515625" style="32" customWidth="1"/>
+    <col min="1" max="1" width="54.5546875" style="32" customWidth="1"/>
+    <col min="2" max="2" width="50.33203125" style="32" customWidth="1"/>
     <col min="3" max="3" width="21" style="32" customWidth="1"/>
-    <col min="4" max="4" width="36.5703125" style="32" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="32" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="32"/>
+    <col min="4" max="4" width="36.5546875" style="32" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="32" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -46899,7 +46919,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="47.25">
+    <row r="9" spans="1:5" ht="46.8">
       <c r="A9" s="30" t="s">
         <v>2822</v>
       </c>
@@ -46916,7 +46936,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="47.25">
+    <row r="10" spans="1:5" ht="46.8">
       <c r="A10" s="34" t="s">
         <v>2825</v>
       </c>
@@ -46967,7 +46987,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="31.5">
+    <row r="13" spans="1:5" ht="31.2">
       <c r="A13" s="30" t="s">
         <v>2708</v>
       </c>
@@ -47035,7 +47055,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="47.25">
+    <row r="17" spans="1:5" ht="46.8">
       <c r="A17" s="30" t="s">
         <v>1224</v>
       </c>
@@ -47086,7 +47106,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="31.5">
+    <row r="20" spans="1:5" ht="31.2">
       <c r="A20" s="34" t="s">
         <v>2845</v>
       </c>
@@ -47120,7 +47140,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="31.5">
+    <row r="22" spans="1:5" ht="31.2">
       <c r="A22" s="30" t="s">
         <v>2847</v>
       </c>
@@ -47341,7 +47361,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="63">
+    <row r="35" spans="1:5" ht="62.4">
       <c r="A35" s="31" t="s">
         <v>2867</v>
       </c>
@@ -47409,7 +47429,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="31.5">
+    <row r="39" spans="1:5" ht="31.2">
       <c r="A39" s="30" t="s">
         <v>2870</v>
       </c>
@@ -47477,7 +47497,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.5">
+    <row r="43" spans="1:5" ht="31.2">
       <c r="A43" s="30" t="s">
         <v>2881</v>
       </c>
@@ -47681,7 +47701,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="78.75">
+    <row r="55" spans="1:5" ht="78">
       <c r="A55" s="34" t="s">
         <v>2870</v>
       </c>
@@ -47919,7 +47939,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.5">
+    <row r="69" spans="1:5" ht="31.2">
       <c r="A69" s="30" t="s">
         <v>2870</v>
       </c>
@@ -47987,7 +48007,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="63">
+    <row r="73" spans="1:5" ht="62.4">
       <c r="A73" s="30" t="s">
         <v>2930</v>
       </c>
@@ -48233,7 +48253,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="31.5">
+    <row r="88" spans="1:5" ht="31.2">
       <c r="A88" s="34" t="s">
         <v>2881</v>
       </c>
@@ -48335,7 +48355,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.5">
+    <row r="94" spans="1:5" ht="31.2">
       <c r="A94" s="34" t="s">
         <v>2957</v>
       </c>
@@ -48352,7 +48372,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.5">
+    <row r="95" spans="1:5" ht="31.2">
       <c r="A95" s="34" t="s">
         <v>2960</v>
       </c>
@@ -48386,7 +48406,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="78.75">
+    <row r="97" spans="1:5" ht="78">
       <c r="A97" s="34" t="s">
         <v>2965</v>
       </c>
@@ -48403,7 +48423,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.5">
+    <row r="98" spans="1:5" ht="31.2">
       <c r="A98" s="30" t="s">
         <v>2967</v>
       </c>
@@ -48454,7 +48474,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="31.5">
+    <row r="101" spans="1:5" ht="31.2">
       <c r="A101" s="41" t="s">
         <v>2972</v>
       </c>
@@ -48573,7 +48593,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="63">
+    <row r="108" spans="1:5" ht="62.4">
       <c r="A108" s="34" t="s">
         <v>2984</v>
       </c>
@@ -48644,14 +48664,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E113"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="54.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="54.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -49895,7 +49915,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5" ht="28.8">
       <c r="A74" s="4" t="s">
         <v>2757</v>
       </c>
@@ -50184,7 +50204,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="45">
+    <row r="91" spans="1:5" ht="43.2">
       <c r="A91" s="4" t="s">
         <v>2774</v>
       </c>
@@ -50422,7 +50442,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="75">
+    <row r="105" spans="1:5" ht="72">
       <c r="A105" s="4" t="s">
         <v>2708</v>
       </c>
@@ -50439,7 +50459,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="30">
+    <row r="106" spans="1:5" ht="28.8">
       <c r="A106" s="4" t="s">
         <v>2799</v>
       </c>
@@ -50473,7 +50493,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="30">
+    <row r="108" spans="1:5" ht="28.8">
       <c r="A108" s="4" t="s">
         <v>2803</v>
       </c>
@@ -50594,14 +50614,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51351,14 +51371,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M50"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="43.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="43.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51752,7 +51772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="30">
+    <row r="24" spans="1:5" ht="28.8">
       <c r="A24" s="4" t="s">
         <v>39</v>
       </c>
@@ -51939,7 +51959,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="30">
+    <row r="35" spans="1:13" ht="28.8">
       <c r="A35" s="4" t="s">
         <v>2564</v>
       </c>
@@ -52235,13 +52255,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E242"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -52329,7 +52349,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30">
+    <row r="6" spans="1:5" ht="28.8">
       <c r="A6" s="4" t="s">
         <v>77</v>
       </c>
@@ -52567,7 +52587,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="30">
+    <row r="20" spans="1:5">
       <c r="A20" s="4" t="s">
         <v>101</v>
       </c>
@@ -52890,7 +52910,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="30">
+    <row r="39" spans="1:5" ht="28.8">
       <c r="A39" s="4" t="s">
         <v>136</v>
       </c>
@@ -52907,7 +52927,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="4" t="s">
         <v>138</v>
       </c>
@@ -52924,7 +52944,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="30">
+    <row r="41" spans="1:5" ht="28.8">
       <c r="A41" s="4" t="s">
         <v>140</v>
       </c>
@@ -52941,7 +52961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="30">
+    <row r="42" spans="1:5" ht="28.8">
       <c r="A42" s="4" t="s">
         <v>141</v>
       </c>
@@ -52975,7 +52995,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5" ht="28.8">
       <c r="A44" s="4" t="s">
         <v>144</v>
       </c>
@@ -53213,7 +53233,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="30">
+    <row r="58" spans="1:5">
       <c r="A58" s="4" t="s">
         <v>167</v>
       </c>
@@ -53230,7 +53250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="30">
+    <row r="59" spans="1:5" ht="28.8">
       <c r="A59" s="4" t="s">
         <v>169</v>
       </c>
@@ -53400,7 +53420,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="30">
+    <row r="69" spans="1:5" ht="28.8">
       <c r="A69" s="4" t="s">
         <v>187</v>
       </c>
@@ -53485,7 +53505,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5">
       <c r="A74" s="4" t="s">
         <v>196</v>
       </c>
@@ -53638,7 +53658,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="30">
+    <row r="83" spans="1:5">
       <c r="A83" s="4" t="s">
         <v>213</v>
       </c>
@@ -53825,7 +53845,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="30">
+    <row r="94" spans="1:5">
       <c r="A94" s="4" t="s">
         <v>231</v>
       </c>
@@ -53927,7 +53947,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="30">
+    <row r="100" spans="1:5">
       <c r="A100" s="4" t="s">
         <v>240</v>
       </c>
@@ -53944,7 +53964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="30">
+    <row r="101" spans="1:5" ht="28.8">
       <c r="A101" s="4" t="s">
         <v>242</v>
       </c>
@@ -54097,7 +54117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="30">
+    <row r="110" spans="1:5">
       <c r="A110" s="4" t="s">
         <v>256</v>
       </c>
@@ -54114,7 +54134,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="30">
+    <row r="111" spans="1:5" ht="28.8">
       <c r="A111" s="4" t="s">
         <v>258</v>
       </c>
@@ -54199,7 +54219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="30">
+    <row r="116" spans="1:5">
       <c r="A116" s="4" t="s">
         <v>267</v>
       </c>
@@ -54250,7 +54270,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="30">
+    <row r="119" spans="1:5" ht="28.8">
       <c r="A119" s="4">
         <v>1961</v>
       </c>
@@ -54522,7 +54542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="30">
+    <row r="135" spans="1:5">
       <c r="A135" s="4" t="s">
         <v>298</v>
       </c>
@@ -54675,7 +54695,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="30">
+    <row r="144" spans="1:5" ht="28.8">
       <c r="A144" s="4" t="s">
         <v>311</v>
       </c>
@@ -54743,7 +54763,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="30">
+    <row r="148" spans="1:5">
       <c r="A148" s="4" t="s">
         <v>298</v>
       </c>
@@ -54777,7 +54797,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="30">
+    <row r="150" spans="1:5" ht="28.8">
       <c r="A150" s="4" t="s">
         <v>317</v>
       </c>
@@ -54794,7 +54814,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="30">
+    <row r="151" spans="1:5">
       <c r="A151" s="4" t="s">
         <v>318</v>
       </c>
@@ -55049,7 +55069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="30">
+    <row r="166" spans="1:5">
       <c r="A166" s="4" t="s">
         <v>339</v>
       </c>
@@ -55219,7 +55239,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="30">
+    <row r="176" spans="1:5">
       <c r="A176" s="4" t="s">
         <v>351</v>
       </c>
@@ -55270,7 +55290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="30">
+    <row r="179" spans="1:5" ht="28.8">
       <c r="A179" s="4" t="s">
         <v>357</v>
       </c>
@@ -55355,7 +55375,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="30">
+    <row r="184" spans="1:5">
       <c r="A184" s="4" t="s">
         <v>298</v>
       </c>
@@ -55440,7 +55460,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="30">
+    <row r="189" spans="1:5">
       <c r="A189" s="4" t="s">
         <v>371</v>
       </c>
@@ -56018,7 +56038,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="30">
+    <row r="223" spans="1:5">
       <c r="A223" s="4" t="s">
         <v>422</v>
       </c>
@@ -56378,12 +56398,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E85"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -56522,7 +56542,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30">
+    <row r="9" spans="1:5" ht="28.8">
       <c r="A9" s="2" t="s">
         <v>462</v>
       </c>
@@ -57049,7 +57069,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="2" t="s">
         <v>496</v>
       </c>
@@ -57389,7 +57409,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="30">
+    <row r="60" spans="1:5" ht="28.8">
       <c r="A60" s="2" t="s">
         <v>496</v>
       </c>
@@ -57406,7 +57426,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="30">
+    <row r="61" spans="1:5" ht="28.8">
       <c r="A61" s="2" t="s">
         <v>496</v>
       </c>
@@ -57423,7 +57443,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="30">
+    <row r="62" spans="1:5" ht="28.8">
       <c r="A62" s="2" t="s">
         <v>526</v>
       </c>
@@ -57508,7 +57528,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5">
       <c r="A67" s="2" t="s">
         <v>532</v>
       </c>
@@ -57661,7 +57681,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="30">
+    <row r="76" spans="1:5" ht="28.8">
       <c r="A76" s="2" t="s">
         <v>542</v>
       </c>
@@ -57678,7 +57698,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="30">
+    <row r="77" spans="1:5" ht="28.8">
       <c r="A77" s="2" t="s">
         <v>543</v>
       </c>
@@ -57729,7 +57749,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="30">
+    <row r="80" spans="1:5" ht="28.8">
       <c r="A80" s="2" t="s">
         <v>545</v>
       </c>
@@ -57851,12 +57871,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E81"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -58335,7 +58355,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="30">
+    <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
         <v>581</v>
       </c>
@@ -58760,7 +58780,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="30">
+    <row r="54" spans="1:5">
       <c r="A54" s="2" t="s">
         <v>615</v>
       </c>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="185" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0943DA9-381B-4003-84ED-0C9A8D1EB032}"/>
+  <xr:revisionPtr revIDLastSave="196" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3247004-5246-4CB0-9397-447EAFF13A78}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7682" uniqueCount="3287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7689" uniqueCount="3289">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14302,6 +14302,12 @@
   </si>
   <si>
     <t>12/17/26 - 5/21/27</t>
+  </si>
+  <si>
+    <t>EWC Controls, LLC</t>
+  </si>
+  <si>
+    <t>4/1/27 - 6/1/27</t>
   </si>
 </sst>
 </file>
@@ -17819,7 +17825,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E107"/>
+  <dimension ref="A1:E109"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -19646,6 +19652,40 @@
       </c>
       <c r="E107" s="48">
         <v>265</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" s="60" t="s">
+        <v>3081</v>
+      </c>
+      <c r="B108" s="60" t="s">
+        <v>3082</v>
+      </c>
+      <c r="C108" s="58" t="s">
+        <v>394</v>
+      </c>
+      <c r="D108" s="50">
+        <v>46387</v>
+      </c>
+      <c r="E108" s="49">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" s="60" t="s">
+        <v>3287</v>
+      </c>
+      <c r="B109" s="60" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C109" s="58" t="s">
+        <v>394</v>
+      </c>
+      <c r="D109" s="50" t="s">
+        <v>3288</v>
+      </c>
+      <c r="E109" s="49">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="196" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3247004-5246-4CB0-9397-447EAFF13A78}"/>
+  <xr:revisionPtr revIDLastSave="203" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFF84C60-9F2E-4D03-B04F-9496AA46E837}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7689" uniqueCount="3289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7697" uniqueCount="3290">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14308,6 +14308,9 @@
   </si>
   <si>
     <t>4/1/27 - 6/1/27</t>
+  </si>
+  <si>
+    <t>11/28/26 - 12/31/26</t>
   </si>
 </sst>
 </file>
@@ -17207,10 +17210,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17825,7 +17824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E109"/>
+  <dimension ref="A1:E111"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -19686,6 +19685,40 @@
       </c>
       <c r="E109" s="49">
         <v>71</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="31.2">
+      <c r="A110" s="48" t="s">
+        <v>3231</v>
+      </c>
+      <c r="B110" s="48" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C110" s="49" t="s">
+        <v>394</v>
+      </c>
+      <c r="D110" s="50" t="s">
+        <v>3289</v>
+      </c>
+      <c r="E110" s="48">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" s="60" t="s">
+        <v>3261</v>
+      </c>
+      <c r="B111" s="60" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C111" s="58" t="s">
+        <v>394</v>
+      </c>
+      <c r="D111" s="50" t="s">
+        <v>3262</v>
+      </c>
+      <c r="E111" s="49">
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="203" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFF84C60-9F2E-4D03-B04F-9496AA46E837}"/>
+  <xr:revisionPtr revIDLastSave="206" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B33119E3-E1EE-48F0-A324-F4B99E0BBF05}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7697" uniqueCount="3290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7697" uniqueCount="3292">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14311,6 +14311,12 @@
   </si>
   <si>
     <t>11/28/26 - 12/31/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Culinaire </t>
+  </si>
+  <si>
+    <t>12/31/26 - 1/1/27</t>
   </si>
 </sst>
 </file>
@@ -17210,6 +17216,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -19344,7 +19354,7 @@
         <v>3262</v>
       </c>
       <c r="E89" s="49">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -19705,20 +19715,20 @@
       </c>
     </row>
     <row r="111" spans="1:5">
-      <c r="A111" s="60" t="s">
-        <v>3261</v>
-      </c>
-      <c r="B111" s="60" t="s">
-        <v>1540</v>
-      </c>
-      <c r="C111" s="58" t="s">
+      <c r="A111" s="48" t="s">
+        <v>3290</v>
+      </c>
+      <c r="B111" s="48" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C111" s="49" t="s">
         <v>394</v>
       </c>
       <c r="D111" s="50" t="s">
-        <v>3262</v>
-      </c>
-      <c r="E111" s="49">
-        <v>66</v>
+        <v>3291</v>
+      </c>
+      <c r="E111" s="48">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="206" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B33119E3-E1EE-48F0-A324-F4B99E0BBF05}"/>
+  <xr:revisionPtr revIDLastSave="219" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09CA4D9C-4A90-4C3F-A6B8-1F55EA38BE40}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7697" uniqueCount="3292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7707" uniqueCount="3296">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14317,6 +14317,18 @@
   </si>
   <si>
     <t>12/31/26 - 1/1/27</t>
+  </si>
+  <si>
+    <t>Sumitomo Mitsui Banking Corporation</t>
+  </si>
+  <si>
+    <t>10/1/26-10/13/26</t>
+  </si>
+  <si>
+    <t>Hillsdale</t>
+  </si>
+  <si>
+    <t>Dr. Praeger's Sensible Foods LLC</t>
   </si>
 </sst>
 </file>
@@ -17834,7 +17846,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:E114"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -19729,6 +19741,57 @@
       </c>
       <c r="E111" s="48">
         <v>75</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="31.2">
+      <c r="A112" s="48" t="s">
+        <v>3292</v>
+      </c>
+      <c r="B112" s="48" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C112" s="49" t="s">
+        <v>419</v>
+      </c>
+      <c r="D112" s="50" t="s">
+        <v>3293</v>
+      </c>
+      <c r="E112" s="48">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" s="60" t="s">
+        <v>3229</v>
+      </c>
+      <c r="B113" s="60" t="s">
+        <v>3294</v>
+      </c>
+      <c r="C113" s="58" t="s">
+        <v>419</v>
+      </c>
+      <c r="D113" s="50">
+        <v>46389</v>
+      </c>
+      <c r="E113" s="49">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" s="58" t="s">
+        <v>3295</v>
+      </c>
+      <c r="B114" s="60" t="s">
+        <v>2601</v>
+      </c>
+      <c r="C114" s="58" t="s">
+        <v>419</v>
+      </c>
+      <c r="D114" s="50">
+        <v>46386</v>
+      </c>
+      <c r="E114" s="49">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -57937,7 +58000,7 @@
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="19" fitToHeight="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="40" fitToHeight="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="219" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09CA4D9C-4A90-4C3F-A6B8-1F55EA38BE40}"/>
+  <xr:revisionPtr revIDLastSave="221" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6623A7E-C941-4416-90D1-AF405E455F31}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7707" uniqueCount="3296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7710" uniqueCount="3297">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14329,6 +14329,9 @@
   </si>
   <si>
     <t>Dr. Praeger's Sensible Foods LLC</t>
+  </si>
+  <si>
+    <t>Atlantic City Linen Supply LLC</t>
   </si>
 </sst>
 </file>
@@ -17846,7 +17849,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E114"/>
+  <dimension ref="A1:E115"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -19655,7 +19658,7 @@
         <v>46374</v>
       </c>
       <c r="E106" s="49">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -19792,6 +19795,23 @@
       </c>
       <c r="E114" s="49">
         <v>168</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="31.2">
+      <c r="A115" s="48" t="s">
+        <v>3296</v>
+      </c>
+      <c r="B115" s="48" t="s">
+        <v>1500</v>
+      </c>
+      <c r="C115" s="49" t="s">
+        <v>419</v>
+      </c>
+      <c r="D115" s="50">
+        <v>46390</v>
+      </c>
+      <c r="E115" s="48">
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="221" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6623A7E-C941-4416-90D1-AF405E455F31}"/>
+  <xr:revisionPtr revIDLastSave="228" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97C31D30-4BA1-4425-A365-86E33A9194C5}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7710" uniqueCount="3297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7713" uniqueCount="3299">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14332,6 +14332,12 @@
   </si>
   <si>
     <t>Atlantic City Linen Supply LLC</t>
+  </si>
+  <si>
+    <t>FRC Balance LLC, DBA The Food Kitchen</t>
+  </si>
+  <si>
+    <t>Hackensack</t>
   </si>
 </sst>
 </file>
@@ -17849,7 +17855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E115"/>
+  <dimension ref="A1:E116"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -19270,7 +19276,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="31.2">
+    <row r="84" spans="1:5" ht="46.8">
       <c r="A84" s="60" t="s">
         <v>3257</v>
       </c>
@@ -19542,7 +19548,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" ht="31.2">
       <c r="A100" s="60" t="s">
         <v>3278</v>
       </c>
@@ -19812,6 +19818,23 @@
       </c>
       <c r="E115" s="48">
         <v>67</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="31.2">
+      <c r="A116" s="60" t="s">
+        <v>3297</v>
+      </c>
+      <c r="B116" s="60" t="s">
+        <v>3298</v>
+      </c>
+      <c r="C116" s="58" t="s">
+        <v>419</v>
+      </c>
+      <c r="D116" s="50">
+        <v>46390</v>
+      </c>
+      <c r="E116" s="49">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="228" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97C31D30-4BA1-4425-A365-86E33A9194C5}"/>
+  <xr:revisionPtr revIDLastSave="235" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AA84316-8ACB-4D55-9745-AA7BA73DEBC6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19092" yWindow="-1596" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7713" uniqueCount="3299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7716" uniqueCount="3300">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14338,6 +14338,9 @@
   </si>
   <si>
     <t>Hackensack</t>
+  </si>
+  <si>
+    <t>Mars Information Services</t>
   </si>
 </sst>
 </file>
@@ -17237,10 +17240,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17855,7 +17854,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E116"/>
+  <dimension ref="A1:E117"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -19066,7 +19065,7 @@
         <v>68</v>
       </c>
       <c r="D71" s="50">
-        <v>46281</v>
+        <v>46301</v>
       </c>
       <c r="E71" s="48">
         <v>69</v>
@@ -19276,7 +19275,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="46.8">
+    <row r="84" spans="1:5" ht="31.2">
       <c r="A84" s="60" t="s">
         <v>3257</v>
       </c>
@@ -19548,7 +19547,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="31.2">
+    <row r="100" spans="1:5">
       <c r="A100" s="60" t="s">
         <v>3278</v>
       </c>
@@ -19835,6 +19834,23 @@
       </c>
       <c r="E116" s="49">
         <v>89</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" s="60" t="s">
+        <v>3299</v>
+      </c>
+      <c r="B117" s="60" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C117" s="58" t="s">
+        <v>419</v>
+      </c>
+      <c r="D117" s="50">
+        <v>46418</v>
+      </c>
+      <c r="E117" s="49">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -59448,7 +59464,7 @@
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="16" fitToHeight="12" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="20" fitToHeight="12" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="235" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AA84316-8ACB-4D55-9745-AA7BA73DEBC6}"/>
+  <xr:revisionPtr revIDLastSave="236" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA14F5C2-D85E-4A71-ABF7-CE9C9F68D863}"/>
   <bookViews>
-    <workbookView xWindow="19092" yWindow="-1596" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7716" uniqueCount="3300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7719" uniqueCount="3301">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14341,6 +14341,9 @@
   </si>
   <si>
     <t>Mars Information Services</t>
+  </si>
+  <si>
+    <t>Teva Pharmaceuticals USA, Inc</t>
   </si>
 </sst>
 </file>
@@ -17240,6 +17243,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17854,7 +17861,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E117"/>
+  <dimension ref="A1:E118"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -19851,6 +19858,23 @@
       </c>
       <c r="E117" s="49">
         <v>55</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="31.2">
+      <c r="A118" s="48" t="s">
+        <v>3300</v>
+      </c>
+      <c r="B118" s="48" t="s">
+        <v>3039</v>
+      </c>
+      <c r="C118" s="49" t="s">
+        <v>419</v>
+      </c>
+      <c r="D118" s="50">
+        <v>46419</v>
+      </c>
+      <c r="E118" s="48">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="236" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA14F5C2-D85E-4A71-ABF7-CE9C9F68D863}"/>
+  <xr:revisionPtr revIDLastSave="244" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1778AFF-E7B9-4DFC-82C3-788762072A32}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -58,17 +58,28 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'2020 WARN Notices'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'2021 WARN Notices'!$1:$1</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7719" uniqueCount="3301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7722" uniqueCount="3302">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14344,6 +14355,9 @@
   </si>
   <si>
     <t>Teva Pharmaceuticals USA, Inc</t>
+  </si>
+  <si>
+    <t>Conduent State &amp; Local Solutions, Inc</t>
   </si>
 </sst>
 </file>
@@ -17861,7 +17875,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E118"/>
+  <dimension ref="A1:E119"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -19282,7 +19296,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="31.2">
+    <row r="84" spans="1:5" ht="46.8">
       <c r="A84" s="60" t="s">
         <v>3257</v>
       </c>
@@ -19554,7 +19568,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" ht="31.2">
       <c r="A100" s="60" t="s">
         <v>3278</v>
       </c>
@@ -19875,6 +19889,23 @@
       </c>
       <c r="E118" s="48">
         <v>61</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="31.2">
+      <c r="A119" s="60" t="s">
+        <v>3301</v>
+      </c>
+      <c r="B119" s="60" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C119" s="58" t="s">
+        <v>419</v>
+      </c>
+      <c r="D119" s="50">
+        <v>46408</v>
+      </c>
+      <c r="E119" s="49">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -58083,7 +58114,7 @@
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="40" fitToHeight="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="20" fitToHeight="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="244" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1778AFF-E7B9-4DFC-82C3-788762072A32}"/>
+  <xr:revisionPtr revIDLastSave="246" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7D89FB9-4B02-493C-AACE-593A8E780539}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19072,7 +19072,7 @@
         <v>46280</v>
       </c>
       <c r="E70" s="48">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -19296,7 +19296,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="46.8">
+    <row r="84" spans="1:5" ht="31.2">
       <c r="A84" s="60" t="s">
         <v>3257</v>
       </c>
@@ -19568,7 +19568,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="31.2">
+    <row r="100" spans="1:5">
       <c r="A100" s="60" t="s">
         <v>3278</v>
       </c>
@@ -19786,7 +19786,7 @@
         <v>3293</v>
       </c>
       <c r="E112" s="48">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="113" spans="1:5">

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="246" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7D89FB9-4B02-493C-AACE-593A8E780539}"/>
+  <xr:revisionPtr revIDLastSave="255" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B67F818-54B4-41AF-9700-590A55903C35}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7722" uniqueCount="3302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7725" uniqueCount="3304">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14358,6 +14358,12 @@
   </si>
   <si>
     <t>Conduent State &amp; Local Solutions, Inc</t>
+  </si>
+  <si>
+    <t>Comcast</t>
+  </si>
+  <si>
+    <t>Atlantic, Burlington, Camden, Cumberland, Gloucester, Mercer, Monmouth, Ocean, and Union counties</t>
   </si>
 </sst>
 </file>
@@ -17875,7 +17881,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E119"/>
+  <dimension ref="A1:E120"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -19906,6 +19912,23 @@
       </c>
       <c r="E119" s="49">
         <v>113</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="78">
+      <c r="A120" s="60" t="s">
+        <v>3302</v>
+      </c>
+      <c r="B120" s="60" t="s">
+        <v>3303</v>
+      </c>
+      <c r="C120" s="58" t="s">
+        <v>419</v>
+      </c>
+      <c r="D120" s="50">
+        <v>46414</v>
+      </c>
+      <c r="E120" s="49">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
